--- a/ChainSentry-EA50-Master-Targets-20261020.xlsx
+++ b/ChainSentry-EA50-Master-Targets-20261020.xlsx
@@ -6480,7 +6480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8339,100 +8339,100 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SPK (Sermaye Piyasasi Kurulu / Capital Markets Board)</t>
+          <t>SAMA (Saudi Central Bank)</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Mahmut Sutcu</t>
+          <t>Ayed Al-Amroq</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Kurul Chairman (appointed 9 May 2026 | removed from office 19-20 Oct 2026, successor not yet named at time of research)</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>https://www.dunya.com (Dunya Gazetesi: "SPK Baskani Mahmut Sutcu ve KGK Baskani Ibrahim Omer Gonul gorevden alindi", 20 Oct 2026 | original appointment: A Haber 9 May 2026, tr.wikipedia.org/wiki/Sermaye_Piyasas%C4%B1_Kurumu)</t>
+          <t>https://news.google.com/rss/search?q=SAMA+governor+Saudi+Arabia</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SPK (Sermaye Piyasasi Kurulu)</t>
+          <t>SAMA (Saudi Central Bank)</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Abdulaziz Abanmi</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Head of digital-assets / crypto licensing division (SPK oversees VASP licensing under Law 7518 | division head not publicly named)</t>
+          <t>Deputy Governor for Payments (oversees regulatory sandbox/fintech policy)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>https://spk.gov.tr/hakkimizda/kurul-baskani</t>
+          <t>https://thefintechtimes.com/inside-samas-strategy-how-saudi-arabia-is-engineering-the-future-of-payments/</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2025-10-05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>MASAK (Financial Crimes Investigation Board)</t>
+          <t>CMA Saudi Arabia</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hasan Kaymak</t>
+          <t>Mazen Al-Sudairi</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>President of MASAK (appointed Feb 2024 | publicly active as MASAK head Oct 2026)</t>
+          <t>Chairman of the Capital Market Authority (appointed by royal decree)</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -8444,190 +8444,190 @@
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr (Anadolu/AHaber 23 Feb 2024 | Anka Haber 14 Oct 2026 "MASAK Baskani Kaymak")</t>
+          <t>https://news.google.com/rss/search?q=Mazen+Al-Sudairi+CMA</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-14</t>
+          <t>ENRICHED 2026-10-20 · 2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>MASAK (Financial Crimes Investigation Board)</t>
+          <t>CMA Saudi Arabia</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Uyum / compliance programme lead (AML compliance supervision directorate | individual not publicly named)</t>
+          <t>head of FinTech Permit/lab not publicly named)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Head of FinTech Permit &amp; innovation lab</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>https://www.masak.gov.tr</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=%22Saudi+Capital+Market+Authority%22+chairman</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>BtcTurk</t>
+          <t>Saudi Financial Investigations Unit (SAFIU)</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Tevfik Kinik</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>CEO of BtcTurk Group Companies (appointed Jan 2026)</t>
+          <t>head not identified in 2025-26 sources)</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>Head of SAFIU (AML/CFT FIU)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr (Anadolu Ajansi &amp; DHA 6 Jan 2026 "BtcTurk'te ust duzey atama" | Fortune Turkey)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-01-06</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=SAFIU+Saudi+financial+investigations</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>BtcTurk</t>
+          <t>Alrajhi Bank</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Fatih Otluoglu</t>
+          <t>Waleed Al-Mogbel</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>CEO of BtcTurk Hisse (brokerage arm)</t>
+          <t>Group CEO (confirmed through 2025 best-CEO award</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t xml:space="preserve"> 2026 results quoted via Abdullah Alrajhi - needs verification)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>https://www.ekonomim.com (Ekonomim &amp; AA 7 Apr 2026)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-04-07</t>
+          <t>ENRICHED 2026-10-20 · https://www.arabnews.com/node/2223976</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>BtcTurk</t>
+          <t>Saudi National Bank (SNB)</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>CCO / MLRO (Head of Compliance / Uyum Muduru - not publicly named)</t>
+          <t>no public digital-assets/CCO lead identified)</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Group CCO / digital assets lead</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>https://www.btcturk.com</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=SNB+%22Saudi+National+Bank%22+chief+compliance+officer</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Paribu</t>
+          <t>stc pay / STC Bank</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Yasin Oral</t>
+          <t>Mohammed Al-Fraih</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>CEO, Paribu (led CoinMENA acquisition Dec 2025 | quoted as CEO in deal coverage)</t>
+          <t>CEO of STC Bank (the licensed evolution of stc pay)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -8639,268 +8639,268 @@
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>https://waya.media/paribu-acquires-majority-stake-in-coinmena-at-240m-valuation/</t>
+          <t>https://news.google.com/rss/search?q=%22stc+pay%22+CEO+appointed</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-12-07</t>
+          <t>ENRICHED 2026-10-20 · 2025-12-29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Paribu</t>
+          <t>stc pay / STC Bank</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Talal Tabba</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Co-founder &amp; CEO, CoinMENA (Paribu group | owns MENA/Jordan expansion - CoinMENA entered Jordan under CBJ JoRegBox sandbox Sep 2026)</t>
+          <t>CCO not publicly named)</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about (co-founder listed) + Khaleej Times (Tabba quoted as CoinMENA CEO) + fintekwins.com Jordan launch 28 Sep 2026</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=%22stc+pay%22+%22chief+compliance+officer%22</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Paribu</t>
+          <t>Qatar Financial Centre Authority</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Mansoor Rashid Al-Khater</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>CCO / Head of Compliance (not publicly named | compliance org spans Paribu + CoinMENA CBB/VARA licences)</t>
+          <t>CEO of QFC (effective 11 Jan 2026, succeeding Yousuf Mohamed Al-Jaida)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>https://www.paribu.com</t>
+          <t>https://www.thepeninsulaqatar.com/article/12/01/2026/qfc-welcomes-mansoor-rashid-al-khater-as-ceo</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2026-01-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Binance TR</t>
+          <t>QFC Regulatory Authority</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Mucahit Donmez</t>
+          <t>Michael Rayan</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>General Manager, Binance TR (active in role Sep 2026)</t>
+          <t>CEO of QFCRA (ran public consultation on Digital Assets Regulations)</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>https://www.teknotalk.com (TeknoTalk 8 Jun 2026: "Binance TR GM Mucahit Donmez" | prior Haberturk Sep 2023)</t>
+          <t>https://ffnews.com/newsarticle/regulatory/qfc-unveils-digital-assets-lab-powered-by-qcb-to-facilitate-open-innovation-in-qatar/</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-16</t>
+          <t>ENRICHED 2026-10-20 · 2023-10-31</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>OKX TR</t>
+          <t>Qatar Financial Centre Authority</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Mehmet Camir</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Chairman of the Board, OKX TR (Turkey JV with OKX)</t>
+          <t>Digital Assets Lab director not publicly named)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>Digital Assets Lab / fintech innovation lead</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>https://www.halktv.com.tr (Halk TV 17 Mar 2026: "OKX TR YK Baskani Mehmet Camir")</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-03-17</t>
+          <t>ENRICHED 2026-10-20 · https://www.ledgerinsights.com/qatar-launches-digital-assets-lab/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>HTTX</t>
+          <t>QNB Group</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>CEO / General Manager (Turkish crypto platform | no 2025-2026 named executive found in news sources - honest gap)</t>
+          <t>digital-asset evaluation lead not publicly named</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t xml:space="preserve"> MoUs signed at Web Summit Qatar 2025)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>https://www.cnbc-e.com (crypto sector coverage | HTTX leadership not covered)</t>
+          <t>Digital assets evaluation lead</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · low</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Garanti BBVA Kripto</t>
+          <t>Qatar Central Bank</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Onur Guven</t>
+          <t>Sheikh Bandar bin Mohammed bin Saoud Al-Thani</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>General Manager, Garanti BBVA Kripto (appointed Jan 2025 | platform still led by him through OTC launch Jul 2026)</t>
+          <t>Governor (since Nov 2021</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t xml:space="preserve"> patron of QFC Digital Assets Lab under QCB Fintech Strategy)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>https://www.haberturk.com (Haberturk 10 Jan 2025 | AA 9 Jul 2026 OTC launch)</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-07-09</t>
+          <t>ENRICHED 2026-10-20 · https://www.qcb.gov.qa/en/Pages/Governor.aspx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Papara / inPay</t>
+          <t>CMA Kuwait</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Ahmet Faruk Karsli</t>
+          <t>Emad Ahmed Tifouni</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Founder &amp; former owner, Papara (arrested Jul 2026 in illegal-betting probe | assets liquidated - Papara sold out of TMSF custody to Emlak Katilim Bankasi Apr 2026)</t>
+          <t>Chairman of CMA Board of Commissioners &amp; Managing Director (Fourth Board, since April 2025)</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -8912,163 +8912,163 @@
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>https://www.evrensel.net (Evrensel 10 Jul 2026 re-arrest | T24/Forbes Turkiye 17 Apr 2026 sale to Emlak Katilim)</t>
+          <t>https://www.cma.gov.kw/en/web/cma/fourth-board</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-07-10</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Papara / inPay</t>
+          <t>CMA Kuwait</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>CEO under new owner (Emlak Katilim Bankasi control) + CCO - not publicly named</t>
+          <t>CMA runs absolute VA ban regime and AML coordination incl. Nazaha MoU 2026)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>VA-framework / AML consultation owner</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>https://www.cnbc-e.com (16 Apr 2026)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-04-16</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=Nazaha+FIU+deepen+alliance</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>FRA (Financial Regulatory Authority)</t>
+          <t>Boubyan Bank</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Islam Azzam</t>
+          <t>Adel Al-Majed</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Chairman, FRA (appointed Mar 2026 | elected IOSCO Vice Chair Apr 2026 | oversees Law 162/2023 virtual-assets regime)</t>
+          <t>Group Vice Chairman &amp; CEO (confirmed in IMF/WB Kuwait banks coverage Oct 2026</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t xml:space="preserve"> a May 2026 Kuwait Times headline references a different surname 'Al-Tuwaijri' as CEO - verify)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>https://enterpriseam.com/egypts-financial-regulatory-authority-appoints-islam-azzam-as-new-head/</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-03-10</t>
+          <t>ENRICHED 2026-10-20 · https://timeskuwait.com/kuwaiti-banks-showcase-financial-strength-at-imf-world-bank-meetings/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>FRA (Financial Regulatory Authority)</t>
+          <t>Boubyan Bank</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Farid</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Former FRA Chairman (through Jan 2026 | superseded by Azzam)</t>
+          <t>digital-assets/compliance head not publicly named)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Head of compliance / digital assets</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com (Feb 2025 "Farid emphasises strengthening non-bank financial sector resilience")</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-01-31</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=Boubyan+Bank+CEO+Kuwait</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>FRA (Financial Regulatory Authority)</t>
+          <t>Financial Services Authority Oman (successor to CMA Oman, est. 2024)</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Dr. Khamis Saif Al Jabri</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Head of AML compliance / virtual-assets supervision under Law 162/2023 (not publicly named)</t>
+          <t>Minister of Economy - Chairman of FSA Board of Directors</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>https://www.fra.org.eg</t>
+          <t>https://www.fsa.gov.om/Home/AboutCMA/BoardofDirectors</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -9080,178 +9080,178 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Egypt FRA-licensed VASP cohort</t>
+          <t>Sohar International</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Abdulwahid Almurshidi</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>First licensed virtual-asset companies (executive-regulations licensing in progress through 2026 | no company names confirmed in 2025-2026 FRA announcements accessible to this research - honest gap)</t>
+          <t>Chief Executive Officer (named Feb 2025)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>https://www.iflr.com (IFLR Egyptian capital market developments, Oct 2025)</t>
+          <t>https://news.google.com/rss/search?q=Sohar+International+CEO+2025</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2025-02-26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Egypt FIU (Unit for Combating Money Laundering and Financing Terrorism, EEFFU)</t>
+          <t>NBO National Bank of Oman</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Khalil (al-Mustashar Ahmed Khalil)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Head of Egypt's AML/CFT Unit (quoted in role Jun-Sep 2026 | MOU with China FIU Aug 2026)</t>
+          <t>CEO and digital-assets lead not verifiable in this pass)</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>CEO / digital assets lead</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>https://www.ahram.org.eg (Akhbar Al-Youm 7 Jul 2026 | SIE 3 Oct 2026 FRA-FIU joint event)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-07</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=National+Bank+of+Oman+digital</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>CIB Egypt / Yomo</t>
+          <t>MENAFATF (secretariat seated Manama, Bahrain)</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Bahrain (MENA body)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Rashwan Hamady</t>
+          <t>Suliman Aljabrin</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>CEO &amp; Managing Director, Yomo (CIB's digital bank - closest CIB digital-assets banking executive)</t>
+          <t>Executive Secretary (since 1 Jan 2021</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t xml:space="preserve"> ex-SAMA Banking Policy Director</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>https://www.fin-tech-gate.com (Fintech Gate / FRA-affiliated portal 20 Aug 2026)</t>
+          <t xml:space="preserve"> verify current incumbency)</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-08-20</t>
+          <t>ENRICHED 2026-10-20 · medium</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>CIB Egypt</t>
+          <t>IFZA (Dubai freezone onboarding)</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Kamran Bader</t>
+          <t>Philipp Conrads (CEO IFZA Dubai) / Jochen Knecht (CEO IFZA Global)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Chief Data, Analytics &amp; AI Officer, CIB Egypt</t>
+          <t>Freezone compliance-services leads</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>https://hrtoday.in (Jun 2026)</t>
+          <t>https://ifza.com/en/leadership/</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-06-04</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Jordan Securities Commission</t>
+          <t>RAKEZ (Ras Al Khaimah Economic Zone)</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Emad Muhammad Abuhaltam</t>
+          <t>Ramy Jallad</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Chairman of the Board of Commissioners &amp; CEO (JSC runs virtual-asset licensing | "Preliminary Approval to Practice Virtual Assets Activities" form live on site)</t>
+          <t>Group CEO of RAKEZ</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -9263,34 +9263,34 @@
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners (official site, last update 19/10/2026)</t>
+          <t>https://usa.chinadaily.com.cn/a/202609/08/WS6a9fd15de4b06d4aa055cf48.html</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+          <t>ENRICHED 2026-10-20 · 2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Jordan Securities Commission</t>
+          <t>DMCC (incl. 500+ crypto member community)</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Elias Ayoub Zoreikat</t>
+          <t>Ahmed Bin Sulayem</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Deputy Chairman, JSC Board of Commissioners</t>
+          <t>Executive Chairman &amp; CEO (Deputy CEO/COO: Feryal Ahmadi)</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -9302,34 +9302,34 @@
       <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+          <t>https://www.dmcc.ae/about-us</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Jordan Securities Commission</t>
+          <t>Deloitte Middle East</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Razan Samih Al-Shafei</t>
+          <t>Simon Cuerden</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Commissioner, JSC Board of Commissioners</t>
+          <t>Leader, Forensic &amp; Financial Crime practice (Middle East)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -9341,34 +9341,34 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+          <t>https://www.consultancy-me.com/news/8737/simon-cuerden-new-leader-of-deloittes-forensic-financial-crime-business</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+          <t>ENRICHED 2026-10-20 · 2025-01-10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Jordan - first regulated VASP</t>
+          <t>FTI Consulting (MENA financial-crime practice)</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Abi-gail Marshman</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA (Paribu group) - first digital-asset trading platform admitted to Central Bank of Jordan JoRegBox regulatory sandbox (Sep 2026, live with CliQ JOD rails) |position-only row (first in-market entity, per Turkish/MENA trade press)</t>
+          <t>Head of Financial Crime for MENA (2022 appointment - verify current)</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -9380,151 +9380,151 @@
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>https://fintekwins.com/paribu-coinmena-ile-urdun-pazarina-girdi/</t>
+          <t>https://www.consultancy-me.com/news/7321/abi-gail-marshman-joins-fti-as-head-of-financial-crime-for-mena</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
+          <t>ENRICHED 2026-10-20 · 2022-09-06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Lebanon FIU (Special Investigation Commission on Money Laundering / SCLC)</t>
+          <t>KPMG Middle East</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Chairperson of SCLC (judicially chaired body | current chair not confirmable from accessible 2025-2026 sources - honest gap | commission active, demanded bank data for 11 persons Sep 2026)</t>
+          <t>no named regional financial-crime practice head found)</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Regional AML/financial-crime practice leader</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>https://www.libnanews.com (24 Sep 2026)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-24</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=KPMG+Middle+East+%22financial+crime%22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Banque du Liban</t>
+          <t>EY Middle East</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Karim Souaid</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Governor of Banque du Liban (appointed Mar 2025 | payments/digital-currency reform agenda | crypto framework owner at recentral bank)</t>
+          <t>EY Crypto Financial Crime CoE is US-listed)</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>Regional AML/financial-crime practice leader</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
       <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>https://www.reuters.com (Reuters 27 Mar 2025 "Lebanon appoints asset manager Karim Souaid as new central bank governor")</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-03-27</t>
+          <t>ENRICHED 2026-10-20 · https://www.ey.com/en_us/services/consulting/financial-crime-crypto-center-of-excellence</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Banque du Liban</t>
+          <t>PwC Middle East</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Head of payments / digital-assets unit (reform-era unit | individual not publicly named)</t>
+          <t>FCS/managed-services financial-crime lead not named)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Regional AML/financial-crime practice leader</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>https://bdl.com.lb</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · https://www.pwc.com/m1/en/services/consulting/financial-crime-management.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>AMMC (Morocco capital-markets regulator)</t>
+          <t>SPK (Sermaye Piyasasi Kurulu / Capital Markets Board)</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Tarik Senhaji</t>
+          <t>Mahmut Sutcu</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Secretary General / de facto head of AMMC (presents 2026 action priorities and speaks as AMMC principal in 2026 press | digital-asset mandate under law 43-21 framework pending implementing texts)</t>
+          <t>Kurul Chairman (appointed 9 May 2026 | removed from office 19-20 Oct 2026, successor not yet named at time of research)</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -9536,24 +9536,24 @@
       <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>https://le360.ma (Le360 23 Jun 2026 "l'AMMC deroule sa strategie" | Le Desk 28 Jan 2026 "Senhaji devoile les priorites d'actions de l'AMMC pour 2026")</t>
+          <t>https://www.dunya.com (Dunya Gazetesi: "SPK Baskani Mahmut Sutcu ve KGK Baskani Ibrahim Omer Gonul gorevden alindi", 20 Oct 2026 | original appointment: A Haber 9 May 2026, tr.wikipedia.org/wiki/Sermaye_Piyasas%C4%B1_Kurumu)</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-30</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>AMMC</t>
+          <t>SPK (Sermaye Piyasasi Kurulu)</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Digital-assets / innovation division lead under law 43-21 (crypto bill draft published Nov 2025 | division head not publicly named)</t>
+          <t>Head of digital-assets / crypto licensing division (SPK oversees VASP licensing under Law 7518 | division head not publicly named)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -9575,34 +9575,34 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>https://medias24.com (3 Nov 2025 avant-projet de loi crypto)</t>
+          <t>https://spk.gov.tr/hakkimizda/kurul-baskani</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-11-03</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>MASAK (Financial Crimes Investigation Board)</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Abdellatif Jouahri</t>
+          <t>Hasan Kaymak</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Wali (Governor), Bank Al-Maghrib (crypto-activities ban stance owner | annual report presented to King Jul 2026 | active through Sep 2026 MPC)</t>
+          <t>President of MASAK (appointed Feb 2024 | publicly active as MASAK head Oct 2026)</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -9614,24 +9614,24 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>https://medias24.com (21 Jul 2026 Jouahri presents BAM annual report to Mohammed VI | SNRT 22 Sep 2026)</t>
+          <t>https://www.aa.com.tr (Anadolu/AHaber 23 Feb 2024 | Anka Haber 14 Oct 2026 "MASAK Baskani Kaymak")</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-22</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>MASAK (Financial Crimes Investigation Board)</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Digital payments / asset tokenisation programme owner (not publicly named)</t>
+          <t>Uyum / compliance programme lead (AML compliance supervision directorate | individual not publicly named)</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -9653,7 +9653,7 @@
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>https://bkam.ma</t>
+          <t>https://www.masak.gov.tr</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -9665,139 +9665,139 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq (CBQ/CBI)</t>
+          <t>BtcTurk</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Nizar (Hussein/Nasir) - full transliteration varies across sources</t>
+          <t>Tevfik Kinik</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Governor of the Central Bank of Iraq (appointed Jun 2026, replacing Ali Al-Alaq | oversaw Oct 2026 dinar re-peg to 1,500 IQD/USD)</t>
+          <t>CEO of BtcTurk Group Companies (appointed Jan 2026)</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>https://enterpriseam.com (24 Jun 2026 "Iraq appoints Nizar Hussein as new central bank governor") + en.wikipedia.org/wiki/Central_Bank_of_Iraq ("Nizar Nasir" infobox, Baghdad Today citation)</t>
+          <t>https://www.aa.com.tr (Anadolu Ajansi &amp; DHA 6 Jan 2026 "BtcTurk'te ust duzey atama" | Fortune Turkey)</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-06-24</t>
+          <t>ENRICHED 2026-10-20 · 2026-01-06</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq</t>
+          <t>BtcTurk</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Fatih Otluoglu</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Deputy Governor for Payments / FX-corridor oversight (dinar-dollar corridor owner | individual not confirmable from accessible sources - corpus-only account, low effort per brief)</t>
+          <t>CEO of BtcTurk Hisse (brokerage arm)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>https://cbi.iq</t>
+          <t>https://www.ekonomim.com (Ekonomim &amp; AA 7 Apr 2026)</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2026-04-07</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>VARA (Dubai)</t>
+          <t>BtcTurk</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Helal Saeed Almarri</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Chairman of Executive Board</t>
+          <t>CCO / MLRO (Head of Compliance / Uyum Muduru - not publicly named)</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
       <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>https://www.vara.ae/en/about-vara/</t>
+          <t>https://www.btcturk.com</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued (subagent leg failed to compile)</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA</t>
+          <t>Paribu</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Talal Tabbaa</t>
+          <t>Yasin Oral</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CEO, Paribu (led CoinMENA acquisition Dec 2025 | quoted as CEO in deal coverage)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -9809,112 +9809,112 @@
       <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about-us</t>
+          <t>https://waya.media/paribu-acquires-majority-stake-in-coinmena-at-240m-valuation/</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2025-12-07</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA</t>
+          <t>Paribu</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Dina Sam'an</t>
+          <t>Talal Tabba</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>Co-founder &amp; CEO, CoinMENA (Paribu group | owns MENA/Jordan expansion - CoinMENA entered Jordan under CBJ JoRegBox sandbox Sep 2026)</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about-us</t>
+          <t>https://www.coinmena.com/en/about (co-founder listed) + Khaleej Times (Tabba quoted as CoinMENA CEO) + fintekwins.com Jordan launch 28 Sep 2026</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA</t>
+          <t>Paribu</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Yazan Barghuthi</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CCO / Head of Compliance (not publicly named | compliance org spans Paribu + CoinMENA CBB/VARA licences)</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about-us</t>
+          <t>https://www.paribu.com</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>DMCC Crypto Centre</t>
+          <t>Binance TR</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>H.E. Mansour Mohamed AlMulla</t>
+          <t>Mucahit Donmez</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Chairman (also Deputy Group CEO, ADQ)</t>
+          <t>General Manager, Binance TR (active in role Sep 2026)</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -9926,49 +9926,1219 @@
       <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>https://dmcc.ae/latest-news</t>
+          <t>https://www.teknotalk.com (TeknoTalk 8 Jun 2026: "Binance TR GM Mucahit Donmez" | prior Haberturk Sep 2023)</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Zand (UAE digital bank)</t>
+          <t>OKX TR</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Mehmet Camir</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>AI-powered bank partnered with CoinMENA fiat-crypto integration = prospect discovery</t>
+          <t>Chairman of the Board, OKX TR (Turkey JV with OKX)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
       <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr">
         <is>
+          <t>https://www.halktv.com.tr (Halk TV 17 Mar 2026: "OKX TR YK Baskani Mehmet Camir")</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>HTTX</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>CEO / General Manager (Turkish crypto platform | no 2025-2026 named executive found in news sources - honest gap)</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cnbc-e.com (crypto sector coverage | HTTX leadership not covered)</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Garanti BBVA Kripto</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Onur Guven</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>General Manager, Garanti BBVA Kripto (appointed Jan 2025 | platform still led by him through OTC launch Jul 2026)</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.haberturk.com (Haberturk 10 Jan 2025 | AA 9 Jul 2026 OTC launch)</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Papara / inPay</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Ahmet Faruk Karsli</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Founder &amp; former owner, Papara (arrested Jul 2026 in illegal-betting probe | assets liquidated - Papara sold out of TMSF custody to Emlak Katilim Bankasi Apr 2026)</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.evrensel.net (Evrensel 10 Jul 2026 re-arrest | T24/Forbes Turkiye 17 Apr 2026 sale to Emlak Katilim)</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Papara / inPay</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>CEO under new owner (Emlak Katilim Bankasi control) + CCO - not publicly named</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cnbc-e.com (16 Apr 2026)</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>FRA (Financial Regulatory Authority)</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Islam Azzam</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Chairman, FRA (appointed Mar 2026 | elected IOSCO Vice Chair Apr 2026 | oversees Law 162/2023 virtual-assets regime)</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>https://enterpriseam.com/egypts-financial-regulatory-authority-appoints-islam-azzam-as-new-head/</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>FRA (Financial Regulatory Authority)</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Mohamed Farid</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Former FRA Chairman (through Jan 2026 | superseded by Azzam)</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dailynewsegypt.com (Feb 2025 "Farid emphasises strengthening non-bank financial sector resilience")</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>FRA (Financial Regulatory Authority)</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Head of AML compliance / virtual-assets supervision under Law 162/2023 (not publicly named)</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fra.org.eg</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Egypt FRA-licensed VASP cohort</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>First licensed virtual-asset companies (executive-regulations licensing in progress through 2026 | no company names confirmed in 2025-2026 FRA announcements accessible to this research - honest gap)</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iflr.com (IFLR Egyptian capital market developments, Oct 2025)</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Egypt FIU (Unit for Combating Money Laundering and Financing Terrorism, EEFFU)</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Ahmed Khalil (al-Mustashar Ahmed Khalil)</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Head of Egypt's AML/CFT Unit (quoted in role Jun-Sep 2026 | MOU with China FIU Aug 2026)</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr"/>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ahram.org.eg (Akhbar Al-Youm 7 Jul 2026 | SIE 3 Oct 2026 FRA-FIU joint event)</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>CIB Egypt / Yomo</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Rashwan Hamady</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>CEO &amp; Managing Director, Yomo (CIB's digital bank - closest CIB digital-assets banking executive)</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fin-tech-gate.com (Fintech Gate / FRA-affiliated portal 20 Aug 2026)</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>CIB Egypt</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Kamran Bader</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Chief Data, Analytics &amp; AI Officer, CIB Egypt</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>https://hrtoday.in (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Securities Commission</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Emad Muhammad Abuhaltam</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Chairman of the Board of Commissioners &amp; CEO (JSC runs virtual-asset licensing | "Preliminary Approval to Practice Virtual Assets Activities" form live on site)</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners (official site, last update 19/10/2026)</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Securities Commission</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Elias Ayoub Zoreikat</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Deputy Chairman, JSC Board of Commissioners</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Securities Commission</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Razan Samih Al-Shafei</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Commissioner, JSC Board of Commissioners</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Jordan - first regulated VASP</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA (Paribu group) - first digital-asset trading platform admitted to Central Bank of Jordan JoRegBox regulatory sandbox (Sep 2026, live with CliQ JOD rails) |position-only row (first in-market entity, per Turkish/MENA trade press)</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>https://fintekwins.com/paribu-coinmena-ile-urdun-pazarina-girdi/</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Lebanon FIU (Special Investigation Commission on Money Laundering / SCLC)</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Chairperson of SCLC (judicially chaired body | current chair not confirmable from accessible 2025-2026 sources - honest gap | commission active, demanded bank data for 11 persons Sep 2026)</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.libnanews.com (24 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Banque du Liban</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Karim Souaid</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Governor of Banque du Liban (appointed Mar 2025 | payments/digital-currency reform agenda | crypto framework owner at recentral bank)</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com (Reuters 27 Mar 2025 "Lebanon appoints asset manager Karim Souaid as new central bank governor")</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2025-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Banque du Liban</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Head of payments / digital-assets unit (reform-era unit | individual not publicly named)</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>https://bdl.com.lb</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>AMMC (Morocco capital-markets regulator)</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Tarik Senhaji</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Secretary General / de facto head of AMMC (presents 2026 action priorities and speaks as AMMC principal in 2026 press | digital-asset mandate under law 43-21 framework pending implementing texts)</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>https://le360.ma (Le360 23 Jun 2026 "l'AMMC deroule sa strategie" | Le Desk 28 Jan 2026 "Senhaji devoile les priorites d'actions de l'AMMC pour 2026")</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>AMMC</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Digital-assets / innovation division lead under law 43-21 (crypto bill draft published Nov 2025 | division head not publicly named)</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>https://medias24.com (3 Nov 2025 avant-projet de loi crypto)</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2025-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Bank Al-Maghrib</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Abdellatif Jouahri</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Wali (Governor), Bank Al-Maghrib (crypto-activities ban stance owner | annual report presented to King Jul 2026 | active through Sep 2026 MPC)</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>https://medias24.com (21 Jul 2026 Jouahri presents BAM annual report to Mohammed VI | SNRT 22 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Bank Al-Maghrib</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Digital payments / asset tokenisation programme owner (not publicly named)</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>https://bkam.ma</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Central Bank of Iraq (CBQ/CBI)</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Nizar (Hussein/Nasir) - full transliteration varies across sources</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Governor of the Central Bank of Iraq (appointed Jun 2026, replacing Ali Al-Alaq | oversaw Oct 2026 dinar re-peg to 1,500 IQD/USD)</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr"/>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>https://enterpriseam.com (24 Jun 2026 "Iraq appoints Nizar Hussein as new central bank governor") + en.wikipedia.org/wiki/Central_Bank_of_Iraq ("Nizar Nasir" infobox, Baghdad Today citation)</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Central Bank of Iraq</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Deputy Governor for Payments / FX-corridor oversight (dinar-dollar corridor owner | individual not confirmable from accessible sources - corpus-only account, low effort per brief)</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr"/>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>https://cbi.iq</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>VARA (Dubai)</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Helal Saeed Almarri</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Chairman of Executive Board</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vara.ae/en/about-vara/</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued (subagent leg failed to compile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Talal Tabbaa</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coinmena.com/en/about-us</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Dina Sam'an</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coinmena.com/en/about-us</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Yazan Barghuthi</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coinmena.com/en/about-us</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>DMCC Crypto Centre</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>H.E. Mansour Mohamed AlMulla</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Chairman (also Deputy Group CEO, ADQ)</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>https://dmcc.ae/latest-news</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Zand (UAE digital bank)</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>AI-powered bank partnered with CoinMENA fiat-crypto integration = prospect discovery</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
           <t>https://www.msn.com/en-us/money/other/uae-digital-bank-zand-offers-coinmena-users-seamless-fiat-to-crypto-integration/ar-AA1LnKaq</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>ENRICHED 2026-10-20 · 2026-09 news</t>
         </is>

--- a/ChainSentry-EA50-Master-Targets-20261020.xlsx
+++ b/ChainSentry-EA50-Master-Targets-20261020.xlsx
@@ -650,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4002,6 +4002,2852 @@
       <c r="K59" s="5" t="inlineStr">
         <is>
           <t>mea-roster AE-02 (T1, high)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>D.01</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>SAMA (Saudi Central Bank)</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Deputy Governor for Payments (sandbox/fintech policy owner) | TRIGGER: SAMA issued first open-banking licences (Lean Technologies first, Mar-Apr 2026) - sandbox pipeline maturing</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>TRIGGER: SAMA issued first open-banking licences (Lean Technologies first, Mar-Apr 2026) - sandbox pipeline maturing</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://thefintechtimes.com/inside-samas-strategy-how-saudi-arabia-is-engineering-the-future-of-payments/ | 2025-10-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>D.02</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>SAMA sandbox Stage-2 entrants</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>First SAMA open-banking licence holder (rulebook.sama.gov.sa regime, sandbox graduate) | Net-new: first licensed open-banking entrant = AML/flow-monitoring obligation from licence date. Other named sandbox entrants not enumerated in accessible sources</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Net-new: first licensed open-banking entrant = AML/flow-monitoring obligation from licence date. Other named sandbox entrants not enumerated in accessible sources</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://thefintechtimes.com/lean-technologies-secures-saudi-arabias-first-open-banking-license-from-sama/ | 2026-03-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>D.03</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>SAMA sandbox Stage-2 entrants</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>SAMA-regulatory-sandbox blockchain payments/custody partnership | NET-NEW TARGET via Riyad Bank: Jeel x Ripple sandbox (payments+custody) Jan-26</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET via Riyad Bank: Jeel x Ripple sandbox (payments+custody) Jan-26</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://www.fintechweekly.com/news/riyad-bank-jeel-ripple-saudi-sandbox-blockchain-payments/ | 2026-01-26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>D.04</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>SAMA sandbox Stage-2 entrants</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Remaining Stage-2 sandbox cohort not publicly enumerated (position-only) | SAMA publishes licence cohorts but no per-company Stage-2 list retrievable this pass - owner follow-up via rulebook.sama.gov.sa</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>SAMA publishes licence cohorts but no per-company Stage-2 list retrievable this pass - owner follow-up via rulebook.sama.gov.sa</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://www.pinsentmasons.com/out-law/news/sama-first-fintechs-open-banking-licences | 2026-04-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>D.05</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>CMA Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Chairman of the Capital Market Authority | TRIGGER: Open World launched KSA's first RWA tokenization Center of Excellence (22-Jan-26) under CMA-adjacent push</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>TRIGGER: Open World launched KSA's first RWA tokenization Center of Excellence (22-Jan-26) under CMA-adjacent push</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=Mazen+Al-Sudairi+CMA | 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>D.06</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Riyad Bank</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Digital-asset/blockchain unit (sandbox entrant) | Riyad Bank is beyond-Al Rajhi/SNB net-new org</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>conf:medium → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Riyad Bank is beyond-Al Rajhi/SNB net-new org</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://www.tradingview.com/news/riyad-bank-jeel-ripple-blockchain-payments-custody/ | 2026-01-26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>D.07</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>ANB (Arab National Bank)</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Digital-asset/compliance lead unfilled (position-only) | No 2026 digital-asset initiative surfaced in this pass - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 digital-asset initiative surfaced in this pass - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=ANB+Saudi+digital+asset+2026 | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>D.08</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Banque Saudi Fransi</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Digital-asset/compliance lead unfilled (position-only) | No 2026 digital-asset initiative surfaced in this pass - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 digital-asset initiative surfaced in this pass - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=%22Banque+Saudi+Fransi%22+digital+asset | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>D.09</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>STC Bank</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>CCO unfilled on record (position-only | yes</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>conf:Al-Fraih = CEO per prior pass) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (low | https://news.google.com/rss/search?q=%22STC+Bank%22+chief+compliance+officer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>D.10</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Financial Investigations Unit (SAFIU)</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Head of SAFIU - still unidentified in 2025-26 public sources (position-only) | No SAFIU head announcement in RSS sweep</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>No SAFIU head announcement in RSS sweep</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=SAFIU+Saudi+financial+investigations | 2026-08-18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>D.11</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Open World (RWA Tokenization CoE)</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Net-new org: Saudi Arabia's first RWA tokenization Center of Excellence | NET-NEW: tokenization CoE launch 22-Jan-26 = screening/fund-tracing demand at coEs and partners</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>conf:medium → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW: tokenization CoE launch 22-Jan-26 = screening/fund-tracing demand at coEs and partners</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://via.google.news/RSS:%22Open+World%22+RWA+tokenization+Saudi+Arabia | 2026-01-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>D.12</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Qatar Financial Centre Authority</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>CEO of QFC (effective 11 Jan 2026) | New-CEO year = programme-review window for digital-assets agenda</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>New-CEO year = programme-review window for digital-assets agenda</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://www.thepeninsulaqatar.com/article/12/01/2026/qfc-welcomes-mansoor-rashid-al-khater-as-ceo | 2026-01-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>D.13</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>QFC Regulatory Authority</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>CEO of QFCRA (Digital Assets Regulations consultation owner) | Stale-role flag - verify tenure before outreach</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>conf:medium → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Stale-role flag - verify tenure before outreach</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://ffnews.com/newsarticle/regulatory/qfc-unveils-digital-assets-lab-powered-by-qcb-to-facilitate-open-innovation-in | 2023-10-31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>D.14</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>QFC Digital Assets LAB - Barzah Capital</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Net-new LAB participant (joining confirmed this week): real-estate tokenisation model | NET-NEW TARGET: Barzah Capital joined QFC Digital Assets Lab 19-20 Oct 2026 - freshest trigger in Gulf</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET: Barzah Capital joined QFC Digital Assets Lab 19-20 Oct 2026 - freshest trigger in Gulf</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr"/>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://tribune.net.net / Qatar Tribune + ZAWYA 19-20 Oct 2026 (via Google News RSS) | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>D.15</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>QFC Digital Assets LAB - Hacken</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Net-new LAB participant (Kyiv-based | yes</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>conf:joined Jan-2025) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr"/>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (medium | https://www.gulf-times.com (via Google News RSS))</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>D.16</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>QNB Group</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Digital-asset lead unfilled (position-only) - digital-asset activity CONFIRMED | TRIGGER: $500m digital bond on HSBC Orion (Nov-25) + first Dubai tokenized MMF with DMZ (Sep-25) - live on-chain issuance = trace/screen surface</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>TRIGGER: $500m digital bond on HSBC Orion (Nov-25) + first Dubai tokenized MMF with DMZ (Sep-25) - live on-chain issuance = trace/screen surface</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr"/>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://www.ledgerinsights.com/qnb-issues-500m-digital-bond-on-hsbc-orion/ | 2025-11-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>D.17</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Dukhan Bank</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Digital-asset lead unfilled (position-only) | No 2026 digital-asset initiative surfaced - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 digital-asset initiative surfaced - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr"/>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=%22Dukhan+Bank%22+digital+asset+tokenization | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>D.18</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Masraf Al Rayan</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Digital-asset lead unfilled (position-only) | No 2026 digital-asset initiative surfaced - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>No 2026 digital-asset initiative surfaced - position-only row per rules</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=%22Masraf+Al+Rayan%22+digital+asset | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>D.19</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House (KFH)</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Digital-assets/compliance lead unfilled (position-only) | TRIGGER: KFH x Beyon Money/Beyon Connect digital-banking collaborations (Feb-May 2026) + 'World's Best Islamic Bank 2026' (17-Oct-26) = digitisation momentum, no named DA seat</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>TRIGGER: KFH x Beyon Money/Beyon Connect digital-banking collaborations (Feb-May 2026) + 'World's Best Islamic Bank 2026' (17-Oct-26) = digitisation momentum, no named DA seat</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr"/>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=Kuwait+Finance+House+digital+compliance+2026 | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>D.20</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Warba Bank</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Compliance/digital-asset lead unfilled (position-only) | TRIGGER: CBK final approval for up to KD100m AT1 sukuk (06-Oct-26) = capital raise, compliance-capacity spend window</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>TRIGGER: CBK final approval for up to KD100m AT1 sukuk (06-Oct-26) = capital raise, compliance-capacity spend window</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr"/>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://www.tradingview.com/news/warba-bank-cbk-at1-sukuk/ | 2026-10-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>D.21</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Boubyan Bank</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Group Vice Chairman &amp; CEO (Al-Tuwaijri surname conflict unresolved) | CCO seat stays UNFILLED (prior pass)</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>conf:medium → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>CCO seat stays UNFILLED (prior pass)</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://timeskuwait.com/kuwaiti-banks-showcase-financial-strength-at-imf-world-bank-meetings/ | 2026-10-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>D.22</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Central Bank of Kuwait (orbit)</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Net-new channel org: runs annual Cybersecurity Leaders Program (6th cohort Aug-2026) | NET-NEW CHANNEL: CBK convenes bank cyber/compliance leadership cohorts = warm-intro route into all KW banks</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>conf:medium → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW CHANNEL: CBK convenes bank cyber/compliance leadership cohorts = warm-intro route into all KW banks</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://ffnews.com (via Google News RSS): CBK sixth Cybersecurity Leaders Program | 2026-08-18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>D.23</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>National Bank of Oman (NBO)</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>CEO still UNFILLED on record (position-only | no</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>conf:leadership page unfetchable this pass) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (low | https://news.google.com/rss/search?q=%22National+Bank+of+Oman%22+CEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>D.24</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Bank Dhofar</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Digital-asset/compliance lead unfilled (position-only) | No Bank Dhofar-specific DA initiative surfaced</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>No Bank Dhofar-specific DA initiative surfaced</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr"/>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=%22Bank+Dhofar%22+digital+asset+2026 | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>D.25</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Omantel / Beyon (fintech orbit)</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Net-new channel partner: Beyon Money powers KFH (KW) and NBO/Ooredoo payment rails in Oman | NET-NEW: Beyon Money/Beyon Connect is cross-Gulf bank fintech rails partner = channel/SI path, not buyer</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>conf:medium → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW: Beyon Money/Beyon Connect is cross-Gulf bank fintech rails partner = channel/SI path, not buyer</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr"/>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://intlbm.com (via Google News RSS): KFH collaborates with Beyon Money | 2026-02-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>D.26</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Sohar International</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Net-new org: Omantel partnership to accelerate Oman digital economy (18-Aug-26) + expat banking proposition (20-Oct-26) | NET-NEW TARGET replacing weak Bank Dhofar signal: two dated 2026 digitisation triggers, expat-remittance flows = fund-tracing fit</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>conf:medium → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET replacing weak Bank Dhofar signal: two dated 2026 digitisation triggers, expat-remittance flows = fund-tracing fit</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://ffnews.com (via Google News RSS): Sohar International &amp; Omantel partner | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>D.27</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>CMA Oman (virtual-asset consultation)</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>NET-NEW TARGET — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Consultation owner unfilled (position-only) | NO-TRIGGER NOTE: Oct-2026 sweep found Oman-specific virtual-asset consultation NOT confirmable - UAE CMA consultation (Jul-26) dominated results</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>NO-TRIGGER NOTE: Oct-2026 sweep found Oman-specific virtual-asset consultation NOT confirmable - UAE CMA consultation (Jul-26) dominated results</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>RESTORE-PROP (needs Hadri nod)</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>Gulf-T2 sweep 2026-10-21 (https://news.google.com/rss/search?q=Oman+%22virtual+asset%22+CMA+regulation+2026 | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>D.28</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Central Bank of Bahrain</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Governor (per 2022 appointment — NOT re-verified this pass | no</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>conf:all search engines blocked) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr"/>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low | https://www.cbb.gov.bh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>D.29</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Bitarus</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>(Founder/CEO — unverified 'Joseph Farah' NOT confirmed | 2026-10-21</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>conf:left blank per rule) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>D.30</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Alaan</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>(CEO/Founder — not confirmable this pass | 2026-10-21</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>conf:all engines blocked) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr"/>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>D.31</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Gan</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>(CEO — not confirmable this pass | 2026-10-21</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>conf:note: master roster rates Gan tier:T3 conf:low, not T2) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr"/>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>D.32</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Liquid (Binance regional)</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>(Regional head — not confirmable</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>conf:premise flag: Liquid is Binance Japan's custody arm → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr"/>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ('Bahrain regional custody arm' framing in roster needs reconciliation) | low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>D.33</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder | Triggers on record: Paribu acquisition (up to $240M) integration live</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Triggers on record: Paribu acquisition (up to $240M) integration live</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr"/>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (https://www.coinmena.com/en/about-us | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>D.34</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr"/>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (https://www.coinmena.com/en/about-us | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>D.35</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>conf:high → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (https://www.coinmena.com/en/about-us | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>D.36</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>(Post-Paribu compliance/integration owner — not publicly named | 2026-10-20</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>conf:Paribu CCO seat also UNFILLED on roster → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr"/>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (compliance org spans Paribu + CoinMENA CBB/VARA licences) | low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>D.37</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>RAKBANK</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>(Stablecoin programme lead — not confirmable</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>conf:AED stablecoin in-principle approval confirmed on record, named owner not published → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (ping RAKBANK Group Head of Digital Banking seat) | low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>D.38</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Mashreq</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>(Digital-asset head — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr"/>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>D.39</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>(Custody/digital-assets lead — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr"/>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>D.40</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>ADIB</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>(Digital-asset lead — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr"/>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>D.41</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>ADCB</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>(Digital-asset lead — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>D.42</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>280x</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>(Founders/CEO — VARA-licensed tokenization exchange | 2026-10-21</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>conf:names not confirmable this pass) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr"/>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>D.43</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Securitize ME</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>(GM/head of Middle East entity — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr"/>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>D.44</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Bitget (MEA)</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>CEO (global | no</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>conf:MENA-specific MD not publicly named) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr"/>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (high)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>D.45</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Crypto.com</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>(MENA GM — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr"/>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>D.46</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>CoinDCX</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>(MENA CEO — not confirmable | 2026-10-20</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>conf:entry vehicle = reported BitOasis acquisition) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr"/>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (medium)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>D.47</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Kraken ME (Payward FZCO)</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>(ME GM — 'Benjamin Ampen' NOT verifiable this pass | 2026-10-21</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>conf:left blank) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr"/>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>D.48</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Police (cyber/economic crimes)</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>(Cyber/economic-crimes commander — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr"/>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>D.49</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Police (cyber directorate)</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>(Cyber directorate head — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr"/>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>D.50</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>ADGM FSRA</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>(Digital-assets lead — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr"/>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>D.51</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>KPMG Middle East</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>(Regional AML/financial-crime practice head — UNFILLED | no</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>conf:name not found this pass) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr"/>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low | https://news.google.com/rss)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>D.52</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>PwC Middle East</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>(FCS/managed-services financial-crime lead — UNFILLED) | Channel row — position-only already on roster</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>Channel row — position-only already on roster</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr"/>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (https://www.pwc.com/m1 | 2026-10-20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>D.53</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>EY Middle East</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>(Regional AML/financial-crime practice head — UNFILLED | no</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>conf:EY Crypto Financial Crime CoE is US-listed) → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr"/>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 (low | https://www.ey.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>T2-DEPTH</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>D.54</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>RedCompliance</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>depth on existing T2 lane — T2-market pass 21-Oct</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>(Principal — not confirmable this pass) | no</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>conf:low → Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Depth-enrich (existing-lane)</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr"/>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>AE/BH-T2 sweep 2026-10-21 ()</t>
         </is>
       </c>
     </row>
@@ -6480,7 +9326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8144,22 +10990,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>OKX (Middle East FZE)</t>
+          <t>SAMA (Saudi Central Bank)</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Mauricio Beugelmans</t>
+          <t>Abdulaziz Abanmi</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Chief Legal Officer — UAE regulatory-approval journey</t>
+          <t>Deputy Governor for Payments (sandbox/fintech policy owner)</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -8171,34 +11017,34 @@
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>(news sweep batch1-3, salvaged)</t>
+          <t>https://thefintechtimes.com/inside-samas-strategy-how-saudi-arabia-is-engineering-the-future-of-payments/</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>T2-DEPTH 21-Oct · 2025-10-05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Bitget (MEA)</t>
+          <t>SAMA sandbox Stage-2 entrants</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Gracy Chen</t>
+          <t>Lean Technologies</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>CEO (mid-year address, tokenization+AI vision)</t>
+          <t>First SAMA open-banking licence holder (rulebook.sama.gov.sa regime, sandbox graduate)</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -8210,34 +11056,34 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>(news sweep, salvaged)</t>
+          <t>https://thefintechtimes.com/lean-technologies-secures-saudi-arabias-first-open-banking-license-from-sama/</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>T2-DEPTH 21-Oct · 2026-03-27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Kraken ME (Payward FZCO)</t>
+          <t>SAMA sandbox Stage-2 entrants</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Jeel (Riyad Bank digital-asset subsidiary) + Ripple</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>VARA Full Market Approval granted - AED trading/staking/OTC launch</t>
+          <t>SAMA-regulatory-sandbox blockchain payments/custody partnership</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -8249,24 +11095,24 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>(news sweep, salvaged)</t>
+          <t>https://www.fintechweekly.com/news/riyad-bank-jeel-ripple-saudi-sandbox-blockchain-payments/</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-2026 news</t>
+          <t>T2-DEPTH 21-Oct · 2026-01-26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>BitOasis</t>
+          <t>SAMA sandbox Stage-2 entrants</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>UAE/BH</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8276,70 +11122,70 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Full VASP licence + Bahrain operations launched after CBB licence</t>
+          <t>Remaining Stage-2 sandbox cohort not publicly enumerated (position-only)</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>(news sweep, salvaged)</t>
+          <t>https://www.pinsentmasons.com/out-law/news/sama-first-fintechs-open-banking-licences</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026 news</t>
+          <t>T2-DEPTH 21-Oct · 2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>BitOasis</t>
+          <t>CMA Saudi Arabia</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>UAE/BH</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Mazen Al-Sudairi</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>CoinDCX acquisition reported (alongside EmNBD majority-owner door - reconcile before outreach)</t>
+          <t>Chairman of the Capital Market Authority</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>(news sweep, salvaged)</t>
+          <t>https://news.google.com/rss/search?q=Mazen+Al-Sudairi+CMA</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026 news</t>
+          <t>T2-DEPTH 21-Oct · 2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SAMA (Saudi Central Bank)</t>
+          <t>Riyad Bank</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -8349,12 +11195,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Ayed Al-Amroq</t>
+          <t>Jeel x Ripple sandbox team (named lead unfilled)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Digital-asset/blockchain unit (sandbox entrant)</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8366,19 +11212,19 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/search?q=SAMA+governor+Saudi+Arabia</t>
+          <t>https://www.tradingview.com/news/riyad-bank-jeel-ripple-blockchain-payments-custody/</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+          <t>T2-DEPTH 21-Oct · 2026-01-26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SAMA (Saudi Central Bank)</t>
+          <t>ANB (Arab National Bank)</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -8388,36 +11234,36 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Abdulaziz Abanmi</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Deputy Governor for Payments (oversees regulatory sandbox/fintech policy)</t>
+          <t>Digital-asset/compliance lead unfilled (position-only)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>https://thefintechtimes.com/inside-samas-strategy-how-saudi-arabia-is-engineering-the-future-of-payments/</t>
+          <t>https://news.google.com/rss/search?q=ANB+Saudi+digital+asset+2026</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-10-05</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>CMA Saudi Arabia</t>
+          <t>Banque Saudi Fransi</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -8427,36 +11273,36 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Mazen Al-Sudairi</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Chairman of the Capital Market Authority (appointed by royal decree)</t>
+          <t>Digital-asset/compliance lead unfilled (position-only)</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/search?q=Mazen+Al-Sudairi+CMA</t>
+          <t>https://news.google.com/rss/search?q=%22Banque+Saudi+Fransi%22+digital+asset</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-08-13</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>CMA Saudi Arabia</t>
+          <t>STC Bank</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -8466,17 +11312,17 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>head of FinTech Permit/lab not publicly named)</t>
+          <t>CCO unfilled on record (position-only</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Head of FinTech Permit &amp; innovation lab</t>
+          <t>Al-Fraih = CEO per prior pass)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
@@ -8488,7 +11334,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=%22Saudi+Capital+Market+Authority%22+chairman</t>
+          <t>T2-DEPTH 21-Oct · https://news.google.com/rss/search?q=%22STC+Bank%22+chief+compliance+officer</t>
         </is>
       </c>
     </row>
@@ -8505,36 +11351,36 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>head not identified in 2025-26 sources)</t>
+          <t>Head of SAFIU - still unidentified in 2025-26 public sources (position-only)</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Head of SAFIU (AML/CFT FIU)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>https://news.google.com/rss/search?q=SAFIU+Saudi+financial+investigations</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=SAFIU+Saudi+financial+investigations</t>
+          <t>T2-DEPTH 21-Oct · 2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Alrajhi Bank</t>
+          <t>Open World (RWA Tokenization CoE)</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -8544,153 +11390,153 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Waleed Al-Mogbel</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Group CEO (confirmed through 2025 best-CEO award</t>
+          <t>Net-new org: Saudi Arabia's first RWA tokenization Center of Excellence</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026 results quoted via Abdullah Alrajhi - needs verification)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>https://via.google.news/RSS:%22Open+World%22+RWA+tokenization+Saudi+Arabia</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://www.arabnews.com/node/2223976</t>
+          <t>T2-DEPTH 21-Oct · 2026-01-22</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Saudi National Bank (SNB)</t>
+          <t>Qatar Financial Centre Authority</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>Mansoor Rashid Al-Khater</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>no public digital-assets/CCO lead identified)</t>
+          <t>CEO of QFC (effective 11 Jan 2026)</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Group CCO / digital assets lead</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>https://www.thepeninsulaqatar.com/article/12/01/2026/qfc-welcomes-mansoor-rashid-al-khater-as-ceo</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=SNB+%22Saudi+National+Bank%22+chief+compliance+officer</t>
+          <t>T2-DEPTH 21-Oct · 2026-01-12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>stc pay / STC Bank</t>
+          <t>QFC Regulatory Authority</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Mohammed Al-Fraih</t>
+          <t>Michael Rayan</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>CEO of STC Bank (the licensed evolution of stc pay)</t>
+          <t>CEO of QFCRA (Digital Assets Regulations consultation owner)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/search?q=%22stc+pay%22+CEO+appointed</t>
+          <t>https://ffnews.com/newsarticle/regulatory/qfc-unveils-digital-assets-lab-powered-by-qcb-to-facilitate-open-innovation-in-qatar/</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-12-29</t>
+          <t>T2-DEPTH 21-Oct · 2023-10-31</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>stc pay / STC Bank</t>
+          <t>QFC Digital Assets LAB - Barzah Capital</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>CCO not publicly named)</t>
+          <t>Net-new LAB participant (joining confirmed this week): real-estate tokenisation model</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>https://tribune.net.net / Qatar Tribune + ZAWYA 19-20 Oct 2026 (via Google News RSS)</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=%22stc+pay%22+%22chief+compliance+officer%22</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Qatar Financial Centre Authority</t>
+          <t>QFC Digital Assets LAB - Hacken</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -8700,36 +11546,36 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Mansoor Rashid Al-Khater</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>CEO of QFC (effective 11 Jan 2026, succeeding Yousuf Mohamed Al-Jaida)</t>
+          <t>Net-new LAB participant (Kyiv-based</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>joined Jan-2025)</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>https://www.thepeninsulaqatar.com/article/12/01/2026/qfc-welcomes-mansoor-rashid-al-khater-as-ceo</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-01-12</t>
+          <t>T2-DEPTH 21-Oct · https://www.gulf-times.com (via Google News RSS)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>QFC Regulatory Authority</t>
+          <t>QNB Group</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -8739,36 +11585,36 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Michael Rayan</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>CEO of QFCRA (ran public consultation on Digital Assets Regulations)</t>
+          <t>Digital-asset lead unfilled (position-only) - digital-asset activity CONFIRMED</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>https://ffnews.com/newsarticle/regulatory/qfc-unveils-digital-assets-lab-powered-by-qcb-to-facilitate-open-innovation-in-qatar/</t>
+          <t>https://www.ledgerinsights.com/qnb-issues-500m-digital-bond-on-hsbc-orion/</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2023-10-31</t>
+          <t>T2-DEPTH 21-Oct · 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Qatar Financial Centre Authority</t>
+          <t>Dukhan Bank</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -8778,36 +11624,36 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Digital Assets Lab director not publicly named)</t>
+          <t>Digital-asset lead unfilled (position-only)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Digital Assets Lab / fintech innovation lead</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>https://news.google.com/rss/search?q=%22Dukhan+Bank%22+digital+asset+tokenization</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://www.ledgerinsights.com/qatar-launches-digital-assets-lab/</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>QNB Group</t>
+          <t>Masraf Al Rayan</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -8817,75 +11663,75 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>digital-asset evaluation lead not publicly named</t>
+          <t>Digital-asset lead unfilled (position-only)</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MoUs signed at Web Summit Qatar 2025)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Digital assets evaluation lead</t>
+          <t>https://news.google.com/rss/search?q=%22Masraf+Al+Rayan%22+digital+asset</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · low</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Qatar Central Bank</t>
+          <t>Kuwait Finance House (KFH)</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Sheikh Bandar bin Mohammed bin Saoud Al-Thani</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Governor (since Nov 2021</t>
+          <t>Digital-assets/compliance lead unfilled (position-only)</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> patron of QFC Digital Assets Lab under QCB Fintech Strategy)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>https://news.google.com/rss/search?q=Kuwait+Finance+House+digital+compliance+2026</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://www.qcb.gov.qa/en/Pages/Governor.aspx</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>CMA Kuwait</t>
+          <t>Warba Bank</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -8895,36 +11741,36 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Emad Ahmed Tifouni</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Chairman of CMA Board of Commissioners &amp; Managing Director (Fourth Board, since April 2025)</t>
+          <t>Compliance/digital-asset lead unfilled (position-only)</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>https://www.cma.gov.kw/en/web/cma/fourth-board</t>
+          <t>https://www.tradingview.com/news/warba-bank-cbk-at1-sukuk/</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>CMA Kuwait</t>
+          <t>Boubyan Bank</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -8934,36 +11780,36 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>Adel Al-Majed</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>CMA runs absolute VA ban regime and AML coordination incl. Nazaha MoU 2026)</t>
+          <t>Group Vice Chairman &amp; CEO (Al-Tuwaijri surname conflict unresolved)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>VA-framework / AML consultation owner</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>https://timeskuwait.com/kuwaiti-banks-showcase-financial-strength-at-imf-world-bank-meetings/</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=Nazaha+FIU+deepen+alliance</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Boubyan Bank</t>
+          <t>Central Bank of Kuwait (orbit)</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -8973,56 +11819,56 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Adel Al-Majed</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Group Vice Chairman &amp; CEO (confirmed in IMF/WB Kuwait banks coverage Oct 2026</t>
+          <t>Net-new channel org: runs annual Cybersecurity Leaders Program (6th cohort Aug-2026)</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a May 2026 Kuwait Times headline references a different surname 'Al-Tuwaijri' as CEO - verify)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>https://ffnews.com (via Google News RSS): CBK sixth Cybersecurity Leaders Program</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://timeskuwait.com/kuwaiti-banks-showcase-financial-strength-at-imf-world-bank-meetings/</t>
+          <t>T2-DEPTH 21-Oct · 2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Boubyan Bank</t>
+          <t>National Bank of Oman (NBO)</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>digital-assets/compliance head not publicly named)</t>
+          <t>CEO still UNFILLED on record (position-only</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Head of compliance / digital assets</t>
+          <t>leadership page unfetchable this pass)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
@@ -9034,14 +11880,14 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=Boubyan+Bank+CEO+Kuwait</t>
+          <t>T2-DEPTH 21-Oct · https://news.google.com/rss/search?q=%22National+Bank+of+Oman%22+CEO</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Financial Services Authority Oman (successor to CMA Oman, est. 2024)</t>
+          <t>Bank Dhofar</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -9051,36 +11897,36 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Dr. Khamis Saif Al Jabri</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Minister of Economy - Chairman of FSA Board of Directors</t>
+          <t>Digital-asset/compliance lead unfilled (position-only)</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>https://www.fsa.gov.om/Home/AboutCMA/BoardofDirectors</t>
+          <t>https://news.google.com/rss/search?q=%22Bank+Dhofar%22+digital+asset+2026</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Sohar International</t>
+          <t>Omantel / Beyon (fintech orbit)</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -9090,12 +11936,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Abdulwahid Almurshidi</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Chief Executive Officer (named Feb 2025)</t>
+          <t>Net-new channel partner: Beyon Money powers KFH (KW) and NBO/Ooredoo payment rails in Oman</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -9107,19 +11953,19 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/search?q=Sohar+International+CEO+2025</t>
+          <t>https://intlbm.com (via Google News RSS): KFH collaborates with Beyon Money</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-02-26</t>
+          <t>T2-DEPTH 21-Oct · 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>NBO National Bank of Oman</t>
+          <t>Sohar International</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -9129,129 +11975,129 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>CEO and digital-assets lead not verifiable in this pass)</t>
+          <t>Net-new org: Omantel partnership to accelerate Oman digital economy (18-Aug-26) + expat banking proposition (20-Oct-26)</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>CEO / digital assets lead</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>https://ffnews.com (via Google News RSS): Sohar International &amp; Omantel partner</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=National+Bank+of+Oman+digital</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>MENAFATF (secretariat seated Manama, Bahrain)</t>
+          <t>CMA Oman (virtual-asset consultation)</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Bahrain (MENA body)</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Suliman Aljabrin</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Executive Secretary (since 1 Jan 2021</t>
+          <t>Consultation owner unfilled (position-only)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ex-SAMA Banking Policy Director</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> verify current incumbency)</t>
+          <t>https://news.google.com/rss/search?q=Oman+%22virtual+asset%22+CMA+regulation+2026</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · medium</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>IFZA (Dubai freezone onboarding)</t>
+          <t>Central Bank of Bahrain</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Philipp Conrads (CEO IFZA Dubai) / Jochen Knecht (CEO IFZA Global)</t>
+          <t>Sheikh Abdulrahman Al Wafi</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Freezone compliance-services leads</t>
+          <t>Governor (per 2022 appointment — NOT re-verified this pass</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>all search engines blocked)</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>https://ifza.com/en/leadership/</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>T2-DEPTH 21-Oct · https://www.cbb.gov.bh</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>RAKEZ (Ras Al Khaimah Economic Zone)</t>
+          <t>CoinMENA</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Ramy Jallad</t>
+          <t>Talal Tabbaa</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Group CEO of RAKEZ</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -9263,34 +12109,34 @@
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>https://usa.chinadaily.com.cn/a/202609/08/WS6a9fd15de4b06d4aa055cf48.html</t>
+          <t>https://www.coinmena.com/en/about-us</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-08</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>DMCC (incl. 500+ crypto member community)</t>
+          <t>CoinMENA</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Bin Sulayem</t>
+          <t>Dina Sam'an</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Executive Chairman &amp; CEO (Deputy CEO/COO: Feryal Ahmadi)</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -9302,34 +12148,34 @@
       <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>https://www.dmcc.ae/about-us</t>
+          <t>https://www.coinmena.com/en/about-us</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Deloitte Middle East</t>
+          <t>CoinMENA</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Simon Cuerden</t>
+          <t>Yazan Barghuthi</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Leader, Forensic &amp; Financial Crime practice (Middle East)</t>
+          <t>Co-Founder</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -9341,19 +12187,19 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>https://www.consultancy-me.com/news/8737/simon-cuerden-new-leader-of-deloittes-forensic-financial-crime-business</t>
+          <t>https://www.coinmena.com/en/about-us</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-01-10</t>
+          <t>T2-DEPTH 21-Oct · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>FTI Consulting (MENA financial-crime practice)</t>
+          <t>Bitget (MEA)</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -9363,36 +12209,36 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Abi-gail Marshman</t>
+          <t>Gracy Chen</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Head of Financial Crime for MENA (2022 appointment - verify current)</t>
+          <t>CEO (global</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>MENA-specific MD not publicly named)</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>https://www.consultancy-me.com/news/7321/abi-gail-marshman-joins-fti-as-head-of-financial-crime-for-mena</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2022-09-06</t>
+          <t>T2-DEPTH 21-Oct</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>KPMG Middle East</t>
+          <t>OKX (Middle East FZE)</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -9402,75 +12248,75 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>Mauricio Beugelmans</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>no named regional financial-crime practice head found)</t>
+          <t>Chief Legal Officer — UAE regulatory-approval journey</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Regional AML/financial-crime practice leader</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>(news sweep batch1-3, salvaged)</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=KPMG+Middle+East+%22financial+crime%22</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>EY Middle East</t>
+          <t>Bitget (MEA)</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>Gracy Chen</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>EY Crypto Financial Crime CoE is US-listed)</t>
+          <t>CEO (mid-year address, tokenization+AI vision)</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Regional AML/financial-crime practice leader</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
       <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>(news sweep, salvaged)</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://www.ey.com/en_us/services/consulting/financial-crime-crypto-center-of-excellence</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>PwC Middle East</t>
+          <t>Kraken ME (Payward FZCO)</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -9480,51 +12326,51 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>UNFILLED (position-only</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>FCS/managed-services financial-crime lead not named)</t>
+          <t>VARA Full Market Approval granted - AED trading/staking/OTC launch</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Regional AML/financial-crime practice leader</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>(news sweep, salvaged)</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · https://www.pwc.com/m1/en/services/consulting/financial-crime-management.html</t>
+          <t>ENRICHED 2026-10-20 · 2025-2026 news</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>SPK (Sermaye Piyasasi Kurulu / Capital Markets Board)</t>
+          <t>BitOasis</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>UAE/BH</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Mahmut Sutcu</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Kurul Chairman (appointed 9 May 2026 | removed from office 19-20 Oct 2026, successor not yet named at time of research)</t>
+          <t>Full VASP licence + Bahrain operations launched after CBB licence</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -9536,24 +12382,24 @@
       <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>https://www.dunya.com (Dunya Gazetesi: "SPK Baskani Mahmut Sutcu ve KGK Baskani Ibrahim Omer Gonul gorevden alindi", 20 Oct 2026 | original appointment: A Haber 9 May 2026, tr.wikipedia.org/wiki/Sermaye_Piyasas%C4%B1_Kurumu)</t>
+          <t>(news sweep, salvaged)</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2026 news</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>SPK (Sermaye Piyasasi Kurulu)</t>
+          <t>BitOasis</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>UAE/BH</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -9563,124 +12409,124 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Head of digital-assets / crypto licensing division (SPK oversees VASP licensing under Law 7518 | division head not publicly named)</t>
+          <t>CoinDCX acquisition reported (alongside EmNBD majority-owner door - reconcile before outreach)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>https://spk.gov.tr/hakkimizda/kurul-baskani</t>
+          <t>(news sweep, salvaged)</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2026 news</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>MASAK (Financial Crimes Investigation Board)</t>
+          <t>SAMA (Saudi Central Bank)</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Hasan Kaymak</t>
+          <t>Ayed Al-Amroq</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>President of MASAK (appointed Feb 2024 | publicly active as MASAK head Oct 2026)</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr (Anadolu/AHaber 23 Feb 2024 | Anka Haber 14 Oct 2026 "MASAK Baskani Kaymak")</t>
+          <t>https://news.google.com/rss/search?q=SAMA+governor+Saudi+Arabia</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-14</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>MASAK (Financial Crimes Investigation Board)</t>
+          <t>SAMA (Saudi Central Bank)</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Abdulaziz Abanmi</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Uyum / compliance programme lead (AML compliance supervision directorate | individual not publicly named)</t>
+          <t>Deputy Governor for Payments (oversees regulatory sandbox/fintech policy)</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>https://www.masak.gov.tr</t>
+          <t>https://thefintechtimes.com/inside-samas-strategy-how-saudi-arabia-is-engineering-the-future-of-payments/</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2025-10-05</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>BtcTurk</t>
+          <t>CMA Saudi Arabia</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Tevfik Kinik</t>
+          <t>Mazen Al-Sudairi</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>CEO of BtcTurk Group Companies (appointed Jan 2026)</t>
+          <t>Chairman of the Capital Market Authority (appointed by royal decree)</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -9692,268 +12538,268 @@
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr (Anadolu Ajansi &amp; DHA 6 Jan 2026 "BtcTurk'te ust duzey atama" | Fortune Turkey)</t>
+          <t>https://news.google.com/rss/search?q=Mazen+Al-Sudairi+CMA</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-01-06</t>
+          <t>ENRICHED 2026-10-20 · 2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>BtcTurk</t>
+          <t>CMA Saudi Arabia</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Fatih Otluoglu</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>CEO of BtcTurk Hisse (brokerage arm)</t>
+          <t>head of FinTech Permit/lab not publicly named)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>Head of FinTech Permit &amp; innovation lab</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>https://www.ekonomim.com (Ekonomim &amp; AA 7 Apr 2026)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-04-07</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=%22Saudi+Capital+Market+Authority%22+chairman</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>BtcTurk</t>
+          <t>Saudi Financial Investigations Unit (SAFIU)</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>CCO / MLRO (Head of Compliance / Uyum Muduru - not publicly named)</t>
+          <t>head not identified in 2025-26 sources)</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Head of SAFIU (AML/CFT FIU)</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
       <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>https://www.btcturk.com</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=SAFIU+Saudi+financial+investigations</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Paribu</t>
+          <t>Alrajhi Bank</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Yasin Oral</t>
+          <t>Waleed Al-Mogbel</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>CEO, Paribu (led CoinMENA acquisition Dec 2025 | quoted as CEO in deal coverage)</t>
+          <t>Group CEO (confirmed through 2025 best-CEO award</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t xml:space="preserve"> 2026 results quoted via Abdullah Alrajhi - needs verification)</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>https://waya.media/paribu-acquires-majority-stake-in-coinmena-at-240m-valuation/</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-12-07</t>
+          <t>ENRICHED 2026-10-20 · https://www.arabnews.com/node/2223976</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Paribu</t>
+          <t>Saudi National Bank (SNB)</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Talal Tabba</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Co-founder &amp; CEO, CoinMENA (Paribu group | owns MENA/Jordan expansion - CoinMENA entered Jordan under CBJ JoRegBox sandbox Sep 2026)</t>
+          <t>no public digital-assets/CCO lead identified)</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Group CCO / digital assets lead</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about (co-founder listed) + Khaleej Times (Tabba quoted as CoinMENA CEO) + fintekwins.com Jordan launch 28 Sep 2026</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=SNB+%22Saudi+National+Bank%22+chief+compliance+officer</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Paribu</t>
+          <t>stc pay / STC Bank</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Mohammed Al-Fraih</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>CCO / Head of Compliance (not publicly named | compliance org spans Paribu + CoinMENA CBB/VARA licences)</t>
+          <t>CEO of STC Bank (the licensed evolution of stc pay)</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>https://www.paribu.com</t>
+          <t>https://news.google.com/rss/search?q=%22stc+pay%22+CEO+appointed</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2025-12-29</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Binance TR</t>
+          <t>stc pay / STC Bank</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Mucahit Donmez</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>General Manager, Binance TR (active in role Sep 2026)</t>
+          <t>CCO not publicly named)</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
       <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>https://www.teknotalk.com (TeknoTalk 8 Jun 2026: "Binance TR GM Mucahit Donmez" | prior Haberturk Sep 2023)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-16</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=%22stc+pay%22+%22chief+compliance+officer%22</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>OKX TR</t>
+          <t>Qatar Financial Centre Authority</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Mehmet Camir</t>
+          <t>Mansoor Rashid Al-Khater</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Chairman of the Board, OKX TR (Turkey JV with OKX)</t>
+          <t>CEO of QFC (effective 11 Jan 2026, succeeding Yousuf Mohamed Al-Jaida)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -9965,190 +12811,190 @@
       <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>https://www.halktv.com.tr (Halk TV 17 Mar 2026: "OKX TR YK Baskani Mehmet Camir")</t>
+          <t>https://www.thepeninsulaqatar.com/article/12/01/2026/qfc-welcomes-mansoor-rashid-al-khater-as-ceo</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-03-17</t>
+          <t>ENRICHED 2026-10-20 · 2026-01-12</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>HTTX</t>
+          <t>QFC Regulatory Authority</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Michael Rayan</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>CEO / General Manager (Turkish crypto platform | no 2025-2026 named executive found in news sources - honest gap)</t>
+          <t>CEO of QFCRA (ran public consultation on Digital Assets Regulations)</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
       <c r="G89" s="5" t="inlineStr"/>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>https://www.cnbc-e.com (crypto sector coverage | HTTX leadership not covered)</t>
+          <t>https://ffnews.com/newsarticle/regulatory/qfc-unveils-digital-assets-lab-powered-by-qcb-to-facilitate-open-innovation-in-qatar/</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · 2023-10-31</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Garanti BBVA Kripto</t>
+          <t>Qatar Financial Centre Authority</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Onur Guven</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>General Manager, Garanti BBVA Kripto (appointed Jan 2025 | platform still led by him through OTC launch Jul 2026)</t>
+          <t>Digital Assets Lab director not publicly named)</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Digital Assets Lab / fintech innovation lead</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
       <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>https://www.haberturk.com (Haberturk 10 Jan 2025 | AA 9 Jul 2026 OTC launch)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-07-09</t>
+          <t>ENRICHED 2026-10-20 · https://www.ledgerinsights.com/qatar-launches-digital-assets-lab/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Papara / inPay</t>
+          <t>QNB Group</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Ahmet Faruk Karsli</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Founder &amp; former owner, Papara (arrested Jul 2026 in illegal-betting probe | assets liquidated - Papara sold out of TMSF custody to Emlak Katilim Bankasi Apr 2026)</t>
+          <t>digital-asset evaluation lead not publicly named</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t xml:space="preserve"> MoUs signed at Web Summit Qatar 2025)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>https://www.evrensel.net (Evrensel 10 Jul 2026 re-arrest | T24/Forbes Turkiye 17 Apr 2026 sale to Emlak Katilim)</t>
+          <t>Digital assets evaluation lead</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-07-10</t>
+          <t>ENRICHED 2026-10-20 · low</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Papara / inPay</t>
+          <t>Qatar Central Bank</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Sheikh Bandar bin Mohammed bin Saoud Al-Thani</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>CEO under new owner (Emlak Katilim Bankasi control) + CCO - not publicly named</t>
+          <t>Governor (since Nov 2021</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t xml:space="preserve"> patron of QFC Digital Assets Lab under QCB Fintech Strategy)</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
       <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>https://www.cnbc-e.com (16 Apr 2026)</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-04-16</t>
+          <t>ENRICHED 2026-10-20 · https://www.qcb.gov.qa/en/Pages/Governor.aspx</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>FRA (Financial Regulatory Authority)</t>
+          <t>CMA Kuwait</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Islam Azzam</t>
+          <t>Emad Ahmed Tifouni</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Chairman, FRA (appointed Mar 2026 | elected IOSCO Vice Chair Apr 2026 | oversees Law 162/2023 virtual-assets regime)</t>
+          <t>Chairman of CMA Board of Commissioners &amp; Managing Director (Fourth Board, since April 2025)</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -10160,190 +13006,190 @@
       <c r="G93" s="5" t="inlineStr"/>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>https://enterpriseam.com/egypts-financial-regulatory-authority-appoints-islam-azzam-as-new-head/</t>
+          <t>https://www.cma.gov.kw/en/web/cma/fourth-board</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-03-10</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>FRA (Financial Regulatory Authority)</t>
+          <t>CMA Kuwait</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Farid</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Former FRA Chairman (through Jan 2026 | superseded by Azzam)</t>
+          <t>CMA runs absolute VA ban regime and AML coordination incl. Nazaha MoU 2026)</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>VA-framework / AML consultation owner</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com (Feb 2025 "Farid emphasises strengthening non-bank financial sector resilience")</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-01-31</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=Nazaha+FIU+deepen+alliance</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>FRA (Financial Regulatory Authority)</t>
+          <t>Boubyan Bank</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Adel Al-Majed</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Head of AML compliance / virtual-assets supervision under Law 162/2023 (not publicly named)</t>
+          <t>Group Vice Chairman &amp; CEO (confirmed in IMF/WB Kuwait banks coverage Oct 2026</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t xml:space="preserve"> a May 2026 Kuwait Times headline references a different surname 'Al-Tuwaijri' as CEO - verify)</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
       <c r="G95" s="5" t="inlineStr"/>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>https://www.fra.org.eg</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · https://timeskuwait.com/kuwaiti-banks-showcase-financial-strength-at-imf-world-bank-meetings/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Egypt FRA-licensed VASP cohort</t>
+          <t>Boubyan Bank</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>First licensed virtual-asset companies (executive-regulations licensing in progress through 2026 | no company names confirmed in 2025-2026 FRA announcements accessible to this research - honest gap)</t>
+          <t>digital-assets/compliance head not publicly named)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Head of compliance / digital assets</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>https://www.iflr.com (IFLR Egyptian capital market developments, Oct 2025)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=Boubyan+Bank+CEO+Kuwait</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Egypt FIU (Unit for Combating Money Laundering and Financing Terrorism, EEFFU)</t>
+          <t>Financial Services Authority Oman (successor to CMA Oman, est. 2024)</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Khalil (al-Mustashar Ahmed Khalil)</t>
+          <t>Dr. Khamis Saif Al Jabri</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Head of Egypt's AML/CFT Unit (quoted in role Jun-Sep 2026 | MOU with China FIU Aug 2026)</t>
+          <t>Minister of Economy - Chairman of FSA Board of Directors</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>https://www.ahram.org.eg (Akhbar Al-Youm 7 Jul 2026 | SIE 3 Oct 2026 FRA-FIU joint event)</t>
+          <t>https://www.fsa.gov.om/Home/AboutCMA/BoardofDirectors</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-07</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>CIB Egypt / Yomo</t>
+          <t>Sohar International</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Rashwan Hamady</t>
+          <t>Abdulwahid Almurshidi</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>CEO &amp; Managing Director, Yomo (CIB's digital bank - closest CIB digital-assets banking executive)</t>
+          <t>Chief Executive Officer (named Feb 2025)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -10355,112 +13201,112 @@
       <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>https://www.fin-tech-gate.com (Fintech Gate / FRA-affiliated portal 20 Aug 2026)</t>
+          <t>https://news.google.com/rss/search?q=Sohar+International+CEO+2025</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-08-20</t>
+          <t>ENRICHED 2026-10-20 · 2025-02-26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>CIB Egypt</t>
+          <t>NBO National Bank of Oman</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Kamran Bader</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Chief Data, Analytics &amp; AI Officer, CIB Egypt</t>
+          <t>CEO and digital-assets lead not verifiable in this pass)</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>CEO / digital assets lead</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
       <c r="G99" s="5" t="inlineStr"/>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>https://hrtoday.in (Jun 2026)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-06-04</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=National+Bank+of+Oman+digital</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Jordan Securities Commission</t>
+          <t>MENAFATF (secretariat seated Manama, Bahrain)</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>Bahrain (MENA body)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Emad Muhammad Abuhaltam</t>
+          <t>Suliman Aljabrin</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Chairman of the Board of Commissioners &amp; CEO (JSC runs virtual-asset licensing | "Preliminary Approval to Practice Virtual Assets Activities" form live on site)</t>
+          <t>Executive Secretary (since 1 Jan 2021</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t xml:space="preserve"> ex-SAMA Banking Policy Director</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners (official site, last update 19/10/2026)</t>
+          <t xml:space="preserve"> verify current incumbency)</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+          <t>ENRICHED 2026-10-20 · medium</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Jordan Securities Commission</t>
+          <t>IFZA (Dubai freezone onboarding)</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Elias Ayoub Zoreikat</t>
+          <t>Philipp Conrads (CEO IFZA Dubai) / Jochen Knecht (CEO IFZA Global)</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Deputy Chairman, JSC Board of Commissioners</t>
+          <t>Freezone compliance-services leads</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -10472,34 +13318,34 @@
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+          <t>https://ifza.com/en/leadership/</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Jordan Securities Commission</t>
+          <t>RAKEZ (Ras Al Khaimah Economic Zone)</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Razan Samih Al-Shafei</t>
+          <t>Ramy Jallad</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Commissioner, JSC Board of Commissioners</t>
+          <t>Group CEO of RAKEZ</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -10511,268 +13357,268 @@
       <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+          <t>https://usa.chinadaily.com.cn/a/202609/08/WS6a9fd15de4b06d4aa055cf48.html</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+          <t>ENRICHED 2026-10-20 · 2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Jordan - first regulated VASP</t>
+          <t>DMCC (incl. 500+ crypto member community)</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Ahmed Bin Sulayem</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA (Paribu group) - first digital-asset trading platform admitted to Central Bank of Jordan JoRegBox regulatory sandbox (Sep 2026, live with CliQ JOD rails) |position-only row (first in-market entity, per Turkish/MENA trade press)</t>
+          <t>Executive Chairman &amp; CEO (Deputy CEO/COO: Feryal Ahmadi)</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
       <c r="G103" s="5" t="inlineStr"/>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>https://fintekwins.com/paribu-coinmena-ile-urdun-pazarina-girdi/</t>
+          <t>https://www.dmcc.ae/about-us</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Lebanon FIU (Special Investigation Commission on Money Laundering / SCLC)</t>
+          <t>Deloitte Middle East</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>Simon Cuerden</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Chairperson of SCLC (judicially chaired body | current chair not confirmable from accessible 2025-2026 sources - honest gap | commission active, demanded bank data for 11 persons Sep 2026)</t>
+          <t>Leader, Forensic &amp; Financial Crime practice (Middle East)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
       <c r="G104" s="5" t="inlineStr"/>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>https://www.libnanews.com (24 Sep 2026)</t>
+          <t>https://www.consultancy-me.com/news/8737/simon-cuerden-new-leader-of-deloittes-forensic-financial-crime-business</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-24</t>
+          <t>ENRICHED 2026-10-20 · 2025-01-10</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Banque du Liban</t>
+          <t>FTI Consulting (MENA financial-crime practice)</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Karim Souaid</t>
+          <t>Abi-gail Marshman</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Governor of Banque du Liban (appointed Mar 2025 | payments/digital-currency reform agenda | crypto framework owner at recentral bank)</t>
+          <t>Head of Financial Crime for MENA (2022 appointment - verify current)</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
       <c r="G105" s="5" t="inlineStr"/>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>https://www.reuters.com (Reuters 27 Mar 2025 "Lebanon appoints asset manager Karim Souaid as new central bank governor")</t>
+          <t>https://www.consultancy-me.com/news/7321/abi-gail-marshman-joins-fti-as-head-of-financial-crime-for-mena</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-03-27</t>
+          <t>ENRICHED 2026-10-20 · 2022-09-06</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Banque du Liban</t>
+          <t>KPMG Middle East</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Head of payments / digital-assets unit (reform-era unit | individual not publicly named)</t>
+          <t>no named regional financial-crime practice head found)</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Regional AML/financial-crime practice leader</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr"/>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>https://bdl.com.lb</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+          <t>ENRICHED 2026-10-20 · https://news.google.com/rss/search?q=KPMG+Middle+East+%22financial+crime%22</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>AMMC (Morocco capital-markets regulator)</t>
+          <t>EY Middle East</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Tarik Senhaji</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Secretary General / de facto head of AMMC (presents 2026 action priorities and speaks as AMMC principal in 2026 press | digital-asset mandate under law 43-21 framework pending implementing texts)</t>
+          <t>EY Crypto Financial Crime CoE is US-listed)</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>Regional AML/financial-crime practice leader</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>https://le360.ma (Le360 23 Jun 2026 "l'AMMC deroule sa strategie" | Le Desk 28 Jan 2026 "Senhaji devoile les priorites d'actions de l'AMMC pour 2026")</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-30</t>
+          <t>ENRICHED 2026-10-20 · https://www.ey.com/en_us/services/consulting/financial-crime-crypto-center-of-excellence</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>AMMC</t>
+          <t>PwC Middle East</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>(position-only)</t>
+          <t>UNFILLED (position-only</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Digital-assets / innovation division lead under law 43-21 (crypto bill draft published Nov 2025 | division head not publicly named)</t>
+          <t>FCS/managed-services financial-crime lead not named)</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Regional AML/financial-crime practice leader</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr"/>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>https://medias24.com (3 Nov 2025 avant-projet de loi crypto)</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2025-11-03</t>
+          <t>ENRICHED 2026-10-20 · https://www.pwc.com/m1/en/services/consulting/financial-crime-management.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>SPK (Sermaye Piyasasi Kurulu / Capital Markets Board)</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Abdellatif Jouahri</t>
+          <t>Mahmut Sutcu</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Wali (Governor), Bank Al-Maghrib (crypto-activities ban stance owner | annual report presented to King Jul 2026 | active through Sep 2026 MPC)</t>
+          <t>Kurul Chairman (appointed 9 May 2026 | removed from office 19-20 Oct 2026, successor not yet named at time of research)</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -10784,24 +13630,24 @@
       <c r="G109" s="5" t="inlineStr"/>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>https://medias24.com (21 Jul 2026 Jouahri presents BAM annual report to Mohammed VI | SNRT 22 Sep 2026)</t>
+          <t>https://www.dunya.com (Dunya Gazetesi: "SPK Baskani Mahmut Sutcu ve KGK Baskani Ibrahim Omer Gonul gorevden alindi", 20 Oct 2026 | original appointment: A Haber 9 May 2026, tr.wikipedia.org/wiki/Sermaye_Piyasas%C4%B1_Kurumu)</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-09-22</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>SPK (Sermaye Piyasasi Kurulu)</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -10811,7 +13657,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Digital payments / asset tokenisation programme owner (not publicly named)</t>
+          <t>Head of digital-assets / crypto licensing division (SPK oversees VASP licensing under Law 7518 | division head not publicly named)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -10823,7 +13669,7 @@
       <c r="G110" s="5" t="inlineStr"/>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>https://bkam.ma</t>
+          <t>https://spk.gov.tr/hakkimizda/kurul-baskani</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -10835,51 +13681,51 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq (CBQ/CBI)</t>
+          <t>MASAK (Financial Crimes Investigation Board)</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Nizar (Hussein/Nasir) - full transliteration varies across sources</t>
+          <t>Hasan Kaymak</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Governor of the Central Bank of Iraq (appointed Jun 2026, replacing Ali Al-Alaq | oversaw Oct 2026 dinar re-peg to 1,500 IQD/USD)</t>
+          <t>President of MASAK (appointed Feb 2024 | publicly active as MASAK head Oct 2026)</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr"/>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>https://enterpriseam.com (24 Jun 2026 "Iraq appoints Nizar Hussein as new central bank governor") + en.wikipedia.org/wiki/Central_Bank_of_Iraq ("Nizar Nasir" infobox, Baghdad Today citation)</t>
+          <t>https://www.aa.com.tr (Anadolu/AHaber 23 Feb 2024 | Anka Haber 14 Oct 2026 "MASAK Baskani Kaymak")</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-06-24</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq</t>
+          <t>MASAK (Financial Crimes Investigation Board)</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -10889,7 +13735,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Deputy Governor for Payments / FX-corridor oversight (dinar-dollar corridor owner | individual not confirmable from accessible sources - corpus-only account, low effort per brief)</t>
+          <t>Uyum / compliance programme lead (AML compliance supervision directorate | individual not publicly named)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -10901,7 +13747,7 @@
       <c r="G112" s="5" t="inlineStr"/>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>https://cbi.iq</t>
+          <t>https://www.masak.gov.tr</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
@@ -10913,22 +13759,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>VARA (Dubai)</t>
+          <t>BtcTurk</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Helal Saeed Almarri</t>
+          <t>Tevfik Kinik</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Chairman of Executive Board</t>
+          <t>CEO of BtcTurk Group Companies (appointed Jan 2026)</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -10940,34 +13786,34 @@
       <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>https://www.vara.ae/en/about-vara/</t>
+          <t>https://www.aa.com.tr (Anadolu Ajansi &amp; DHA 6 Jan 2026 "BtcTurk'te ust duzey atama" | Fortune Turkey)</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued (subagent leg failed to compile)</t>
+          <t>ENRICHED 2026-10-20 · 2026-01-06</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA</t>
+          <t>BtcTurk</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Talal Tabbaa</t>
+          <t>Fatih Otluoglu</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CEO of BtcTurk Hisse (brokerage arm)</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -10979,73 +13825,73 @@
       <c r="G114" s="5" t="inlineStr"/>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about-us</t>
+          <t>https://www.ekonomim.com (Ekonomim &amp; AA 7 Apr 2026)</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2026-04-07</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA</t>
+          <t>BtcTurk</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Dina Sam'an</t>
+          <t>(position-only)</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CCO / MLRO (Head of Compliance / Uyum Muduru - not publicly named)</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
       <c r="G115" s="5" t="inlineStr"/>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about-us</t>
+          <t>https://www.btcturk.com</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>CoinMENA</t>
+          <t>Paribu</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Yazan Barghuthi</t>
+          <t>Yasin Oral</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Co-Founder</t>
+          <t>CEO, Paribu (led CoinMENA acquisition Dec 2025 | quoted as CEO in deal coverage)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -11057,63 +13903,63 @@
       <c r="G116" s="5" t="inlineStr"/>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>https://www.coinmena.com/en/about-us</t>
+          <t>https://waya.media/paribu-acquires-majority-stake-in-coinmena-at-240m-valuation/</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2025-12-07</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>DMCC Crypto Centre</t>
+          <t>Paribu</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>H.E. Mansour Mohamed AlMulla</t>
+          <t>Talal Tabba</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Chairman (also Deputy Group CEO, ADQ)</t>
+          <t>Co-founder &amp; CEO, CoinMENA (Paribu group | owns MENA/Jordan expansion - CoinMENA entered Jordan under CBJ JoRegBox sandbox Sep 2026)</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr"/>
       <c r="G117" s="5" t="inlineStr"/>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>https://dmcc.ae/latest-news</t>
+          <t>https://www.coinmena.com/en/about (co-founder listed) + Khaleej Times (Tabba quoted as CoinMENA CEO) + fintekwins.com Jordan launch 28 Sep 2026</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Zand (UAE digital bank)</t>
+          <t>Paribu</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -11123,22 +13969,1270 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>AI-powered bank partnered with CoinMENA fiat-crypto integration = prospect discovery</t>
+          <t>CCO / Head of Compliance (not publicly named | compliance org spans Paribu + CoinMENA CBB/VARA licences)</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
       <c r="G118" s="5" t="inlineStr"/>
       <c r="H118" s="5" t="inlineStr">
         <is>
+          <t>https://www.paribu.com</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Binance TR</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Mucahit Donmez</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>General Manager, Binance TR (active in role Sep 2026)</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>https://www.teknotalk.com (TeknoTalk 8 Jun 2026: "Binance TR GM Mucahit Donmez" | prior Haberturk Sep 2023)</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>OKX TR</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Mehmet Camir</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Chairman of the Board, OKX TR (Turkey JV with OKX)</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>https://www.halktv.com.tr (Halk TV 17 Mar 2026: "OKX TR YK Baskani Mehmet Camir")</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>HTTX</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>CEO / General Manager (Turkish crypto platform | no 2025-2026 named executive found in news sources - honest gap)</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cnbc-e.com (crypto sector coverage | HTTX leadership not covered)</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Garanti BBVA Kripto</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Onur Guven</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>General Manager, Garanti BBVA Kripto (appointed Jan 2025 | platform still led by him through OTC launch Jul 2026)</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>https://www.haberturk.com (Haberturk 10 Jan 2025 | AA 9 Jul 2026 OTC launch)</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Papara / inPay</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Ahmet Faruk Karsli</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Founder &amp; former owner, Papara (arrested Jul 2026 in illegal-betting probe | assets liquidated - Papara sold out of TMSF custody to Emlak Katilim Bankasi Apr 2026)</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.evrensel.net (Evrensel 10 Jul 2026 re-arrest | T24/Forbes Turkiye 17 Apr 2026 sale to Emlak Katilim)</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Papara / inPay</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>CEO under new owner (Emlak Katilim Bankasi control) + CCO - not publicly named</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cnbc-e.com (16 Apr 2026)</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>FRA (Financial Regulatory Authority)</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Islam Azzam</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Chairman, FRA (appointed Mar 2026 | elected IOSCO Vice Chair Apr 2026 | oversees Law 162/2023 virtual-assets regime)</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>https://enterpriseam.com/egypts-financial-regulatory-authority-appoints-islam-azzam-as-new-head/</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>FRA (Financial Regulatory Authority)</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Mohamed Farid</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Former FRA Chairman (through Jan 2026 | superseded by Azzam)</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dailynewsegypt.com (Feb 2025 "Farid emphasises strengthening non-bank financial sector resilience")</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>FRA (Financial Regulatory Authority)</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Head of AML compliance / virtual-assets supervision under Law 162/2023 (not publicly named)</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fra.org.eg</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Egypt FRA-licensed VASP cohort</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>First licensed virtual-asset companies (executive-regulations licensing in progress through 2026 | no company names confirmed in 2025-2026 FRA announcements accessible to this research - honest gap)</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iflr.com (IFLR Egyptian capital market developments, Oct 2025)</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Egypt FIU (Unit for Combating Money Laundering and Financing Terrorism, EEFFU)</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Ahmed Khalil (al-Mustashar Ahmed Khalil)</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Head of Egypt's AML/CFT Unit (quoted in role Jun-Sep 2026 | MOU with China FIU Aug 2026)</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ahram.org.eg (Akhbar Al-Youm 7 Jul 2026 | SIE 3 Oct 2026 FRA-FIU joint event)</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>CIB Egypt / Yomo</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Rashwan Hamady</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>CEO &amp; Managing Director, Yomo (CIB's digital bank - closest CIB digital-assets banking executive)</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fin-tech-gate.com (Fintech Gate / FRA-affiliated portal 20 Aug 2026)</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>CIB Egypt</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Kamran Bader</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Chief Data, Analytics &amp; AI Officer, CIB Egypt</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>https://hrtoday.in (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Securities Commission</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Emad Muhammad Abuhaltam</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Chairman of the Board of Commissioners &amp; CEO (JSC runs virtual-asset licensing | "Preliminary Approval to Practice Virtual Assets Activities" form live on site)</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners (official site, last update 19/10/2026)</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Securities Commission</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Elias Ayoub Zoreikat</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Deputy Chairman, JSC Board of Commissioners</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Securities Commission</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Razan Samih Al-Shafei</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Commissioner, JSC Board of Commissioners</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jsc.gov.jo/page/en/chairman_and_board_of_commissioners</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Jordan - first regulated VASP</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>JO</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA (Paribu group) - first digital-asset trading platform admitted to Central Bank of Jordan JoRegBox regulatory sandbox (Sep 2026, live with CliQ JOD rails) |position-only row (first in-market entity, per Turkish/MENA trade press)</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>https://fintekwins.com/paribu-coinmena-ile-urdun-pazarina-girdi/</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Lebanon FIU (Special Investigation Commission on Money Laundering / SCLC)</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Chairperson of SCLC (judicially chaired body | current chair not confirmable from accessible 2025-2026 sources - honest gap | commission active, demanded bank data for 11 persons Sep 2026)</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>https://www.libnanews.com (24 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Banque du Liban</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Karim Souaid</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Governor of Banque du Liban (appointed Mar 2025 | payments/digital-currency reform agenda | crypto framework owner at recentral bank)</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com (Reuters 27 Mar 2025 "Lebanon appoints asset manager Karim Souaid as new central bank governor")</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2025-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Banque du Liban</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Head of payments / digital-assets unit (reform-era unit | individual not publicly named)</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr"/>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>https://bdl.com.lb</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>AMMC (Morocco capital-markets regulator)</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Tarik Senhaji</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Secretary General / de facto head of AMMC (presents 2026 action priorities and speaks as AMMC principal in 2026 press | digital-asset mandate under law 43-21 framework pending implementing texts)</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr"/>
+      <c r="G139" s="5" t="inlineStr"/>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>https://le360.ma (Le360 23 Jun 2026 "l'AMMC deroule sa strategie" | Le Desk 28 Jan 2026 "Senhaji devoile les priorites d'actions de l'AMMC pour 2026")</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>AMMC</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Digital-assets / innovation division lead under law 43-21 (crypto bill draft published Nov 2025 | division head not publicly named)</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>https://medias24.com (3 Nov 2025 avant-projet de loi crypto)</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2025-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Bank Al-Maghrib</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Abdellatif Jouahri</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Wali (Governor), Bank Al-Maghrib (crypto-activities ban stance owner | annual report presented to King Jul 2026 | active through Sep 2026 MPC)</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>https://medias24.com (21 Jul 2026 Jouahri presents BAM annual report to Mohammed VI | SNRT 22 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Bank Al-Maghrib</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Digital payments / asset tokenisation programme owner (not publicly named)</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr"/>
+      <c r="G142" s="5" t="inlineStr"/>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>https://bkam.ma</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Central Bank of Iraq (CBQ/CBI)</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Nizar (Hussein/Nasir) - full transliteration varies across sources</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Governor of the Central Bank of Iraq (appointed Jun 2026, replacing Ali Al-Alaq | oversaw Oct 2026 dinar re-peg to 1,500 IQD/USD)</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr"/>
+      <c r="G143" s="5" t="inlineStr"/>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>https://enterpriseam.com (24 Jun 2026 "Iraq appoints Nizar Hussein as new central bank governor") + en.wikipedia.org/wiki/Central_Bank_of_Iraq ("Nizar Nasir" infobox, Baghdad Today citation)</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Central Bank of Iraq</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Deputy Governor for Payments / FX-corridor oversight (dinar-dollar corridor owner | individual not confirmable from accessible sources - corpus-only account, low effort per brief)</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr"/>
+      <c r="G144" s="5" t="inlineStr"/>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>https://cbi.iq</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>VARA (Dubai)</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Helal Saeed Almarri</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Chairman of Executive Board</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr"/>
+      <c r="G145" s="5" t="inlineStr"/>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vara.ae/en/about-vara/</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued (subagent leg failed to compile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Talal Tabbaa</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr"/>
+      <c r="G146" s="5" t="inlineStr"/>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coinmena.com/en/about-us</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Dina Sam'an</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr"/>
+      <c r="G147" s="5" t="inlineStr"/>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coinmena.com/en/about-us</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>CoinMENA</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Yazan Barghuthi</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr"/>
+      <c r="G148" s="5" t="inlineStr"/>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coinmena.com/en/about-us</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>DMCC Crypto Centre</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>H.E. Mansour Mohamed AlMulla</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Chairman (also Deputy Group CEO, ADQ)</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr"/>
+      <c r="G149" s="5" t="inlineStr"/>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>https://dmcc.ae/latest-news</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>ENRICHED 2026-10-20 · 2026-10-20 rescued</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Zand (UAE digital bank)</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>(position-only)</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>AI-powered bank partnered with CoinMENA fiat-crypto integration = prospect discovery</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr"/>
+      <c r="G150" s="5" t="inlineStr"/>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
           <t>https://www.msn.com/en-us/money/other/uae-digital-bank-zand-offers-coinmena-users-seamless-fiat-to-crypto-integration/ar-AA1LnKaq</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I150" s="5" t="inlineStr">
         <is>
           <t>ENRICHED 2026-10-20 · 2026-09 news</t>
         </is>

--- a/ChainSentry-EA50-Master-Targets-20261020.xlsx
+++ b/ChainSentry-EA50-Master-Targets-20261020.xlsx
@@ -7940,7 +7940,11 @@
           <t>tier:T2 conf:medium → Expansion-pool</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | ENTITY-NOTE (t2 sweep 21-Oct): Liquid = Binance JAPAN custody arm (Quoine lineage) — "Bahrain regional custody arm" framing reconciled; verify licence entity before outreach</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
